--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/feb-2025.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/feb-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC feb-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC feb-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8235,7 +8235,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10313,7 +10313,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10435,7 +10435,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10740,7 +10740,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10801,7 +10801,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10923,7 +10923,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10984,7 +10984,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11167,7 +11167,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11289,7 +11289,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11350,7 +11350,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11472,7 +11472,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11655,7 +11655,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11777,7 +11777,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11838,7 +11838,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11899,7 +11899,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11960,7 +11960,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12021,7 +12021,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12082,7 +12082,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12143,7 +12143,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12265,7 +12265,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12326,7 +12326,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12387,7 +12387,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12448,7 +12448,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12570,7 +12570,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12631,7 +12631,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12692,7 +12692,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12875,7 +12875,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -12997,7 +12997,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13058,7 +13058,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13180,7 +13180,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13302,7 +13302,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -13363,7 +13363,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13485,7 +13485,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13546,7 +13546,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13607,7 +13607,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13729,7 +13729,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -13790,7 +13790,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13851,7 +13851,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -13912,7 +13912,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -13973,7 +13973,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14034,7 +14034,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14156,7 +14156,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -14217,7 +14217,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -14278,7 +14278,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14339,7 +14339,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">

--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/feb-2025.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/feb-2025.xlsx
@@ -684,7 +684,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +749,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +814,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1001,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1066,11 @@
           <t>77.942.697-1</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1253,11 @@
           <t>77.721.515-9</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1318,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1505,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1570,11 @@
           <t>77.721.515-9</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1696,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2127,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2253,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2379,11 @@
           <t>77.544.929-2</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2627,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2692,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3184,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3371,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3619,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3684,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +3932,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +3997,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4062,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4127,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4192,11 @@
           <t>77.544.929-2</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4257,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4322,11 @@
           <t>76.359.833-0</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4387,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4513,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4700,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4765,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4891,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5017,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5082,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5208,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5273,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5338,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5647,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5834,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +5899,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6086,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6151,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6216,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6281,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6346,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6472,11 @@
           <t>77.721.515-9</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6537,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6663,11 @@
           <t>77.721.515-9</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6728,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6793,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7102,11 @@
           <t>77.820.166-6</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7167,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7293,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7358,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7423,11 @@
           <t>77.721.515-9</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7488,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7553,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +7923,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +7988,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8114,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8423,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8488,11 @@
           <t>76.359.833-0</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8553,11 @@
           <t>77.721.515-9</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +8740,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9049,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9114,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9179,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9244,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9309,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9374,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9561,11 @@
           <t>78.616.370-6</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9687,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +9752,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +9878,11 @@
           <t>77.544.929-2</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +9943,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10008,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10134,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10199,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10326,7 +10634,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10387,7 +10699,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10448,7 +10764,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10509,7 +10829,11 @@
           <t>78.616.370-6</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10570,7 +10894,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10631,7 +10959,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10692,7 +11024,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10814,7 +11150,11 @@
           <t>77.544.929-2</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10875,7 +11215,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10936,7 +11280,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11058,7 +11406,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11363,7 +11715,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11485,7 +11841,11 @@
           <t>77.888.564-6</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11546,7 +11906,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11607,7 +11971,11 @@
           <t>77.312.472-8</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11729,7 +12097,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11790,7 +12162,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11912,7 +12288,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12278,7 +12658,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12400,7 +12784,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12461,7 +12849,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12644,7 +13036,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12705,7 +13101,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12949,7 +13349,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13071,7 +13475,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13193,7 +13601,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13254,7 +13666,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13315,7 +13731,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13376,7 +13796,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13559,7 +13983,11 @@
           <t>77.544.929-2</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13620,7 +14048,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13681,7 +14113,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13742,7 +14178,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13803,7 +14243,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14047,7 +14491,11 @@
           <t>78.254.990-1</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14352,7 +14800,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
